--- a/manual-testing/test-design-techniques/equivalence-partitioning.xlsx
+++ b/manual-testing/test-design-techniques/equivalence-partitioning.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="104">
   <si>
     <t>Test ID</t>
   </si>
@@ -335,6 +335,12 @@
   </si>
   <si>
     <t>Invalid calendar date</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Bu tablo test tasarımı aşamasını göstermektedir. Test execution sonuçları test-cases.xlsx dosyasında takip edilmiştir.</t>
   </si>
 </sst>
 </file>
@@ -344,7 +350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +363,24 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
@@ -602,7 +626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -700,6 +724,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
@@ -1216,6 +1242,20 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10">
@@ -1229,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1487,6 +1527,20 @@
       <c r="G11" s="19"/>
       <c r="H11" s="18"/>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C11">
@@ -1499,7 +1553,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1757,6 +1811,20 @@
       <c r="G11" s="19"/>
       <c r="H11" s="18"/>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C11">
